--- a/data/Base_Similaridade_Tarifarios.xlsx
+++ b/data/Base_Similaridade_Tarifarios.xlsx
@@ -1497,7 +1497,7 @@
         <v>5.208333333333333</v>
       </c>
       <c r="K11">
-        <v>0.8864306784660767</v>
+        <v>0.88659793814433</v>
       </c>
       <c r="L11">
         <v>0.004597701149425287</v>
@@ -1942,7 +1942,7 @@
         <v>5.208333333333333</v>
       </c>
       <c r="K25">
-        <v>0.8864306784660768</v>
+        <v>0.8865979381443301</v>
       </c>
       <c r="L25">
         <v>0.004597701149425287</v>
@@ -2210,7 +2210,7 @@
         <v>4.348776342624065</v>
       </c>
       <c r="K33">
-        <v>0.8976052848885219</v>
+        <v>0.8976897689768977</v>
       </c>
       <c r="L33">
         <v>0.005438477226376614</v>
@@ -2289,7 +2289,7 @@
         <v>4.348776342624065</v>
       </c>
       <c r="K35">
-        <v>0.8976052848885219</v>
+        <v>0.8976897689768977</v>
       </c>
       <c r="L35">
         <v>0.005438477226376614</v>
@@ -2464,7 +2464,7 @@
         <v>4.872156862745098</v>
       </c>
       <c r="K40">
-        <v>0.8846153846153846</v>
+        <v>0.8847457627118644</v>
       </c>
       <c r="L40">
         <v>0.004668534080298786</v>
@@ -2619,7 +2619,7 @@
         <v>5.208333333333333</v>
       </c>
       <c r="K44">
-        <v>0.8864306784660766</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="L44">
         <v>0.004597701149425287</v>
@@ -2666,7 +2666,7 @@
         <v>4.872156862745098</v>
       </c>
       <c r="K45">
-        <v>0.8846153846153847</v>
+        <v>0.8847457627118643</v>
       </c>
       <c r="L45">
         <v>0.004668534080298786</v>
@@ -2873,7 +2873,7 @@
         <v>4.348776342624065</v>
       </c>
       <c r="K51">
-        <v>0.897605284888522</v>
+        <v>0.8976897689768978</v>
       </c>
       <c r="L51">
         <v>0.005438477226376614</v>
@@ -3080,7 +3080,7 @@
         <v>4.348776342624065</v>
       </c>
       <c r="K57">
-        <v>0.897605284888522</v>
+        <v>0.8976897689768978</v>
       </c>
       <c r="L57">
         <v>0.005438477226376614</v>
@@ -3255,7 +3255,7 @@
         <v>5.208333333333333</v>
       </c>
       <c r="K62">
-        <v>0.8864306784660767</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="L62">
         <v>0.004597701149425287</v>
@@ -3669,7 +3669,7 @@
         <v>4.348776342624065</v>
       </c>
       <c r="K74">
-        <v>0.8976052848885218</v>
+        <v>0.8976897689768976</v>
       </c>
       <c r="L74">
         <v>0.005438477226376613</v>
@@ -3780,7 +3780,7 @@
         <v>4.348776342624065</v>
       </c>
       <c r="K77">
-        <v>0.8976052848885219</v>
+        <v>0.8976897689768977</v>
       </c>
       <c r="L77">
         <v>0.005438477226376614</v>
@@ -3847,7 +3847,7 @@
         <v>279.25</v>
       </c>
       <c r="G79">
-        <v>0.9399999999999999</v>
+        <v>0.9403973509933775</v>
       </c>
       <c r="H79">
         <v>0.01257861635220126</v>
@@ -4019,7 +4019,7 @@
         <v>5.208333333333333</v>
       </c>
       <c r="K84">
-        <v>0.8864306784660767</v>
+        <v>0.8865979381443301</v>
       </c>
       <c r="L84">
         <v>0.004597701149425287</v>
@@ -4066,7 +4066,7 @@
         <v>4.872156862745098</v>
       </c>
       <c r="K85">
-        <v>0.8846153846153851</v>
+        <v>0.8847457627118651</v>
       </c>
       <c r="L85">
         <v>0.004668534080298786</v>
@@ -4241,7 +4241,7 @@
         <v>5.208333333333333</v>
       </c>
       <c r="K90">
-        <v>0.8864306784660767</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="L90">
         <v>0.004597701149425287</v>
@@ -4288,7 +4288,7 @@
         <v>4.872156862745098</v>
       </c>
       <c r="K91">
-        <v>0.8846153846153846</v>
+        <v>0.8847457627118644</v>
       </c>
       <c r="L91">
         <v>0.004668534080298786</v>
@@ -4620,7 +4620,7 @@
         <v>4.348776342624065</v>
       </c>
       <c r="K101">
-        <v>0.8976052848885212</v>
+        <v>0.897689768976897</v>
       </c>
       <c r="L101">
         <v>0.005438477226376614</v>
@@ -4667,7 +4667,7 @@
         <v>5.208333333333333</v>
       </c>
       <c r="K102">
-        <v>0.8864306784660768</v>
+        <v>0.8865979381443302</v>
       </c>
       <c r="L102">
         <v>0.004597701149425287</v>
@@ -4714,7 +4714,7 @@
         <v>4.872156862745098</v>
       </c>
       <c r="K103">
-        <v>0.8846153846153846</v>
+        <v>0.8847457627118644</v>
       </c>
       <c r="L103">
         <v>0.004668534080298786</v>
@@ -4857,7 +4857,7 @@
         <v>4.348776342624065</v>
       </c>
       <c r="K107">
-        <v>0.8976052848885219</v>
+        <v>0.8976897689768977</v>
       </c>
       <c r="L107">
         <v>0.005438477226376614</v>
@@ -4904,7 +4904,7 @@
         <v>5.208333333333333</v>
       </c>
       <c r="K108">
-        <v>0.8864306784660767</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="L108">
         <v>0.004597701149425287</v>
@@ -5143,7 +5143,7 @@
         <v>4.348776342624065</v>
       </c>
       <c r="K115">
-        <v>0.8976052848885219</v>
+        <v>0.8976897689768977</v>
       </c>
       <c r="L115">
         <v>0.005438477226376614</v>
@@ -5318,7 +5318,7 @@
         <v>4.348776342624065</v>
       </c>
       <c r="K120">
-        <v>0.897605284888522</v>
+        <v>0.8976897689768978</v>
       </c>
       <c r="L120">
         <v>0.005438477226376614</v>
@@ -5429,7 +5429,7 @@
         <v>4.348776342624065</v>
       </c>
       <c r="K123">
-        <v>0.8976052848885219</v>
+        <v>0.8976897689768977</v>
       </c>
       <c r="L123">
         <v>0.005438477226376614</v>
@@ -5636,7 +5636,7 @@
         <v>4.348776342624065</v>
       </c>
       <c r="K129">
-        <v>0.8976052848885219</v>
+        <v>0.8976897689768977</v>
       </c>
       <c r="L129">
         <v>0.005438477226376614</v>
@@ -5953,7 +5953,7 @@
         <v>616.59</v>
       </c>
       <c r="G139">
-        <v>0.9945054945054945</v>
+        <v>0.9945652173913043</v>
       </c>
       <c r="H139">
         <v>0.004716981132075472</v>
@@ -6093,7 +6093,7 @@
         <v>5.208333333333333</v>
       </c>
       <c r="K143">
-        <v>0.8864306784660768</v>
+        <v>0.8865979381443301</v>
       </c>
       <c r="L143">
         <v>0.004597701149425287</v>
@@ -6140,7 +6140,7 @@
         <v>4.872156862745098</v>
       </c>
       <c r="K144">
-        <v>0.8846153846153847</v>
+        <v>0.8847457627118643</v>
       </c>
       <c r="L144">
         <v>0.004668534080298786</v>
@@ -6330,7 +6330,7 @@
         <v>5.208333333333333</v>
       </c>
       <c r="K149">
-        <v>0.8864306784660767</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="L149">
         <v>0.004597701149425287</v>
@@ -6409,7 +6409,7 @@
         <v>4.348776342624065</v>
       </c>
       <c r="K151">
-        <v>0.8976052848885219</v>
+        <v>0.8976897689768977</v>
       </c>
       <c r="L151">
         <v>0.005438477226376614</v>
@@ -6820,7 +6820,7 @@
         <v>5.208333333333332</v>
       </c>
       <c r="K163">
-        <v>0.8864306784660768</v>
+        <v>0.8865979381443302</v>
       </c>
       <c r="L163">
         <v>0.004597701149425287</v>
@@ -6867,7 +6867,7 @@
         <v>4.872156862745098</v>
       </c>
       <c r="K164">
-        <v>0.8846153846153846</v>
+        <v>0.8847457627118644</v>
       </c>
       <c r="L164">
         <v>0.004668534080298786</v>
@@ -7042,7 +7042,7 @@
         <v>5.208333333333333</v>
       </c>
       <c r="K169">
-        <v>0.8864306784660767</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="L169">
         <v>0.004597701149425287</v>
@@ -7089,7 +7089,7 @@
         <v>4.872156862745098</v>
       </c>
       <c r="K170">
-        <v>0.8846153846153846</v>
+        <v>0.8847457627118644</v>
       </c>
       <c r="L170">
         <v>0.004668534080298786</v>
@@ -7311,7 +7311,7 @@
         <v>4.348776342624065</v>
       </c>
       <c r="K176">
-        <v>0.897605284888522</v>
+        <v>0.8976897689768978</v>
       </c>
       <c r="L176">
         <v>0.005438477226376614</v>
@@ -7390,7 +7390,7 @@
         <v>4.348776342624065</v>
       </c>
       <c r="K178">
-        <v>0.8976052848885212</v>
+        <v>0.897689768976897</v>
       </c>
       <c r="L178">
         <v>0.005438477226376614</v>
@@ -7437,7 +7437,7 @@
         <v>5.208333333333333</v>
       </c>
       <c r="K179">
-        <v>0.8864306784660739</v>
+        <v>0.8865979381443307</v>
       </c>
       <c r="L179">
         <v>0.004597701149425287</v>
@@ -7475,7 +7475,7 @@
         <v>1</v>
       </c>
       <c r="H180">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="I180">
         <v>40</v>
@@ -7484,7 +7484,7 @@
         <v>4.872156862745098</v>
       </c>
       <c r="K180">
-        <v>0.8846153846153844</v>
+        <v>0.8847457627118649</v>
       </c>
       <c r="L180">
         <v>0.004668534080298786</v>
@@ -7659,7 +7659,7 @@
         <v>4.872156862745098</v>
       </c>
       <c r="K185">
-        <v>0.8846153846153847</v>
+        <v>0.8847457627118643</v>
       </c>
       <c r="L185">
         <v>0.004668534080298786</v>
@@ -7881,7 +7881,7 @@
         <v>4.872156862745098</v>
       </c>
       <c r="K191">
-        <v>0.8846153846153846</v>
+        <v>0.8847457627118644</v>
       </c>
       <c r="L191">
         <v>0.004668534080298786</v>
@@ -8120,7 +8120,7 @@
         <v>5.208333333333333</v>
       </c>
       <c r="K198">
-        <v>0.8864306784660768</v>
+        <v>0.88659793814433</v>
       </c>
       <c r="L198">
         <v>0.004597701149425287</v>
@@ -8167,7 +8167,7 @@
         <v>4.872156862745098</v>
       </c>
       <c r="K199">
-        <v>0.8846153846153861</v>
+        <v>0.8847457627118621</v>
       </c>
       <c r="L199">
         <v>0.004668534080298786</v>
@@ -8325,7 +8325,7 @@
         <v>5.208333333333333</v>
       </c>
       <c r="K203">
-        <v>0.8864306784660768</v>
+        <v>0.8865979381443301</v>
       </c>
       <c r="L203">
         <v>0.004597701149425287</v>
@@ -8468,7 +8468,7 @@
         <v>5.208333333333333</v>
       </c>
       <c r="K207">
-        <v>0.8864306784660768</v>
+        <v>0.8865979381443301</v>
       </c>
       <c r="L207">
         <v>0.004597701149425287</v>
@@ -8922,7 +8922,7 @@
         <v>4.348776342624065</v>
       </c>
       <c r="K221">
-        <v>0.8976052848885219</v>
+        <v>0.8976897689768977</v>
       </c>
       <c r="L221">
         <v>0.005438477226376614</v>
@@ -8969,7 +8969,7 @@
         <v>5.208333333333333</v>
       </c>
       <c r="K222">
-        <v>0.8864306784660767</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="L222">
         <v>0.004597701149425287</v>
@@ -9188,7 +9188,7 @@
         <v>4.872156862745098</v>
       </c>
       <c r="K228">
-        <v>0.8846153846153849</v>
+        <v>0.8847457627118641</v>
       </c>
       <c r="L228">
         <v>0.004668534080298786</v>
@@ -9456,7 +9456,7 @@
         <v>4.348776342624065</v>
       </c>
       <c r="K236">
-        <v>0.8976052848885219</v>
+        <v>0.8976897689768977</v>
       </c>
       <c r="L236">
         <v>0.005438477226376614</v>
@@ -9555,7 +9555,7 @@
         <v>207.46</v>
       </c>
       <c r="G239">
-        <v>0.9655172413793104</v>
+        <v>0.9661016949152542</v>
       </c>
       <c r="H239">
         <v>0.015625</v>
@@ -9695,7 +9695,7 @@
         <v>4.348776342624065</v>
       </c>
       <c r="K243">
-        <v>0.897605284888522</v>
+        <v>0.8976897689768978</v>
       </c>
       <c r="L243">
         <v>0.005438477226376614</v>
@@ -10010,7 +10010,7 @@
         <v>4.872156862745098</v>
       </c>
       <c r="K252">
-        <v>0.8846153846153846</v>
+        <v>0.8847457627118644</v>
       </c>
       <c r="L252">
         <v>0.004668534080298786</v>
@@ -10200,7 +10200,7 @@
         <v>4.348776342624065</v>
       </c>
       <c r="K257">
-        <v>0.897605284888522</v>
+        <v>0.8976897689768978</v>
       </c>
       <c r="L257">
         <v>0.005438477226376614</v>
@@ -10343,7 +10343,7 @@
         <v>4.348776342624065</v>
       </c>
       <c r="K261">
-        <v>0.8976052848885219</v>
+        <v>0.8976897689768977</v>
       </c>
       <c r="L261">
         <v>0.005438477226376614</v>
@@ -10454,7 +10454,7 @@
         <v>4.348776342624065</v>
       </c>
       <c r="K264">
-        <v>0.8976052848885219</v>
+        <v>0.8976897689768977</v>
       </c>
       <c r="L264">
         <v>0.005438477226376614</v>
@@ -10533,7 +10533,7 @@
         <v>4.348776342624065</v>
       </c>
       <c r="K266">
-        <v>0.8976052848885219</v>
+        <v>0.8976897689768977</v>
       </c>
       <c r="L266">
         <v>0.005438477226376614</v>
@@ -10928,7 +10928,7 @@
         <v>5.208333333333333</v>
       </c>
       <c r="K276">
-        <v>0.8864306784660767</v>
+        <v>0.8865979381443301</v>
       </c>
       <c r="L276">
         <v>0.004597701149425287</v>
@@ -10975,7 +10975,7 @@
         <v>4.872156862745097</v>
       </c>
       <c r="K277">
-        <v>0.8846153846153845</v>
+        <v>0.8847457627118646</v>
       </c>
       <c r="L277">
         <v>0.004668534080298786</v>
@@ -11276,7 +11276,7 @@
         <v>4.872156862745098</v>
       </c>
       <c r="K285">
-        <v>0.8846153846153846</v>
+        <v>0.8847457627118644</v>
       </c>
       <c r="L285">
         <v>0.004668534080298786</v>
@@ -11597,7 +11597,7 @@
         <v>86.59</v>
       </c>
       <c r="G294">
-        <v>0.6896551724137931</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H294">
         <v>0.02941176470588235</v>
@@ -11609,7 +11609,7 @@
         <v>4.348776342624065</v>
       </c>
       <c r="K294">
-        <v>0.8976052848885212</v>
+        <v>0.897689768976897</v>
       </c>
       <c r="L294">
         <v>0.005438477226376614</v>
@@ -11907,7 +11907,7 @@
         <v>5.208333333333333</v>
       </c>
       <c r="K302">
-        <v>0.8864306784660767</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="L302">
         <v>0.004597701149425287</v>
@@ -11983,7 +11983,7 @@
         <v>4.348776342624065</v>
       </c>
       <c r="K304">
-        <v>0.8976052848885219</v>
+        <v>0.8976897689768977</v>
       </c>
       <c r="L304">
         <v>0.005438477226376614</v>
@@ -12687,7 +12687,7 @@
         <v>3.119343971631205</v>
       </c>
       <c r="K320">
-        <v>0.9481037924151682</v>
+        <v>0.9482071713147411</v>
       </c>
       <c r="L320">
         <v>0.01773049645390071</v>
@@ -14353,7 +14353,7 @@
         <v>94.16</v>
       </c>
       <c r="G370">
-        <v>0.9333333333333333</v>
+        <v>0.9375</v>
       </c>
       <c r="H370">
         <v>0</v>
@@ -15436,7 +15436,7 @@
         <v>1.723593561368209</v>
       </c>
       <c r="K403">
-        <v>0.8857749469214439</v>
+        <v>0.8853989813242783</v>
       </c>
       <c r="L403">
         <v>0.02052313883299799</v>
@@ -15983,7 +15983,7 @@
         <v>2.30114247311828</v>
       </c>
       <c r="K417">
-        <v>0.9437869822485208</v>
+        <v>0.9438700147710486</v>
       </c>
       <c r="L417">
         <v>0.01478494623655914</v>
@@ -16347,7 +16347,7 @@
         <v>0.9588128407026046</v>
       </c>
       <c r="L425">
-        <v>0.02942840973401245</v>
+        <v>0.02999434069043577</v>
       </c>
       <c r="M425">
         <v>0.68</v>
@@ -16482,7 +16482,7 @@
         <v>3.119343971631205</v>
       </c>
       <c r="K428">
-        <v>0.9481037924151696</v>
+        <v>0.9482071713147411</v>
       </c>
       <c r="L428">
         <v>0.01773049645390071</v>
@@ -18221,7 +18221,7 @@
         <v>2.30114247311828</v>
       </c>
       <c r="K480">
-        <v>0.9437869822485205</v>
+        <v>0.9438700147710487</v>
       </c>
       <c r="L480">
         <v>0.01478494623655914</v>
@@ -19040,6 +19040,9 @@
       <c r="F500">
         <v>0</v>
       </c>
+      <c r="G500">
+        <v>1</v>
+      </c>
       <c r="H500">
         <v>0</v>
       </c>
@@ -19954,7 +19957,7 @@
         <v>3.119343971631205</v>
       </c>
       <c r="K526">
-        <v>0.9481037924151696</v>
+        <v>0.9482071713147411</v>
       </c>
       <c r="L526">
         <v>0.01773049645390071</v>

--- a/data/Base_Similaridade_Tarifarios.xlsx
+++ b/data/Base_Similaridade_Tarifarios.xlsx
@@ -1604,7 +1604,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K9">
-        <v>0.8155034324942791</v>
+        <v>0.815270231627109</v>
       </c>
       <c r="L9">
         <v>0.03749002924754054</v>
@@ -1745,7 +1745,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K12">
-        <v>0.8155034324942791</v>
+        <v>0.8152702316271089</v>
       </c>
       <c r="L12">
         <v>0.03749002924754054</v>
@@ -2447,7 +2447,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K27">
-        <v>0.8155034324942786</v>
+        <v>0.8152702316271094</v>
       </c>
       <c r="L27">
         <v>0.03749002924754054</v>
@@ -2823,7 +2823,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K35">
-        <v>0.8422613854475659</v>
+        <v>0.8419399860432663</v>
       </c>
       <c r="L35">
         <v>0.03103448275862069</v>
@@ -2917,7 +2917,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K37">
-        <v>0.8422613854475657</v>
+        <v>0.8419399860432661</v>
       </c>
       <c r="L37">
         <v>0.03103448275862069</v>
@@ -2999,7 +2999,7 @@
         <v>1086.98</v>
       </c>
       <c r="G39">
-        <v>0.7808219178082192</v>
+        <v>0.7702702702702703</v>
       </c>
       <c r="H39">
         <v>0.06521739130434782</v>
@@ -3152,7 +3152,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K42">
-        <v>0.8000494926998271</v>
+        <v>0.7996537224833045</v>
       </c>
       <c r="L42">
         <v>0.03686529098075585</v>
@@ -3199,7 +3199,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K43">
-        <v>0.8251108647450109</v>
+        <v>0.8248337028824835</v>
       </c>
       <c r="L43">
         <v>0.08527696793002916</v>
@@ -3340,7 +3340,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K46">
-        <v>0.8155034324942791</v>
+        <v>0.815270231627109</v>
       </c>
       <c r="L46">
         <v>0.03749002924754054</v>
@@ -3387,7 +3387,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K47">
-        <v>0.8000494926998271</v>
+        <v>0.7996537224833045</v>
       </c>
       <c r="L47">
         <v>0.03686529098075585</v>
@@ -3669,7 +3669,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K53">
-        <v>0.8422613854475651</v>
+        <v>0.8419399860432655</v>
       </c>
       <c r="L53">
         <v>0.03103448275862069</v>
@@ -3716,7 +3716,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K54">
-        <v>0.8000494926998267</v>
+        <v>0.7996537224833045</v>
       </c>
       <c r="L54">
         <v>0.03686529098075585</v>
@@ -3998,7 +3998,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K60">
-        <v>0.8422613854475653</v>
+        <v>0.8419399860432658</v>
       </c>
       <c r="L60">
         <v>0.03103448275862069</v>
@@ -4233,7 +4233,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K65">
-        <v>0.8155034324942791</v>
+        <v>0.815270231627109</v>
       </c>
       <c r="L65">
         <v>0.03749002924754054</v>
@@ -4782,7 +4782,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K77">
-        <v>0.8422613854475659</v>
+        <v>0.8419399860432659</v>
       </c>
       <c r="L77">
         <v>0.03103448275862069</v>
@@ -4923,7 +4923,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K80">
-        <v>0.8422613854475659</v>
+        <v>0.8419399860432658</v>
       </c>
       <c r="L80">
         <v>0.03103448275862069</v>
@@ -5020,7 +5020,7 @@
         <v>0.9380103934669604</v>
       </c>
       <c r="L82">
-        <v>0.03348937702556716</v>
+        <v>0.03384947785379906</v>
       </c>
       <c r="M82">
         <v>18.39</v>
@@ -5252,7 +5252,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K87">
-        <v>0.8155034324942786</v>
+        <v>0.8152702316271094</v>
       </c>
       <c r="L87">
         <v>0.03749002924754054</v>
@@ -5299,7 +5299,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K88">
-        <v>0.8000494926998271</v>
+        <v>0.7996537224833034</v>
       </c>
       <c r="L88">
         <v>0.03686529098075585</v>
@@ -5349,7 +5349,7 @@
         <v>0.9380103934669636</v>
       </c>
       <c r="L89">
-        <v>0.03348937702556716</v>
+        <v>0.03384947785379906</v>
       </c>
       <c r="M89">
         <v>10</v>
@@ -5581,7 +5581,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K94">
-        <v>0.8155034324942791</v>
+        <v>0.815270231627109</v>
       </c>
       <c r="L94">
         <v>0.03749002924754054</v>
@@ -5628,7 +5628,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K95">
-        <v>0.8000494926998267</v>
+        <v>0.7996537224833045</v>
       </c>
       <c r="L95">
         <v>0.03686529098075585</v>
@@ -5675,7 +5675,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K96">
-        <v>0.8251108647450111</v>
+        <v>0.8248337028824834</v>
       </c>
       <c r="L96">
         <v>0.08527696793002916</v>
@@ -5722,7 +5722,7 @@
         <v>0.9380103934669636</v>
       </c>
       <c r="L97">
-        <v>0.03348937702556716</v>
+        <v>0.03384947785379906</v>
       </c>
       <c r="M97">
         <v>1.23</v>
@@ -5910,7 +5910,7 @@
         <v>0.9380103934669667</v>
       </c>
       <c r="L101">
-        <v>0.03348937702556716</v>
+        <v>0.03384947785379906</v>
       </c>
       <c r="M101">
         <v>24.43</v>
@@ -6142,7 +6142,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K106">
-        <v>0.8422613854475647</v>
+        <v>0.8419399860432651</v>
       </c>
       <c r="L106">
         <v>0.03103448275862069</v>
@@ -6189,7 +6189,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K107">
-        <v>0.8155034324942794</v>
+        <v>0.8152702316271097</v>
       </c>
       <c r="L107">
         <v>0.03749002924754054</v>
@@ -6236,7 +6236,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K108">
-        <v>0.8000494926998269</v>
+        <v>0.7996537224833045</v>
       </c>
       <c r="L108">
         <v>0.03686529098075585</v>
@@ -6274,7 +6274,7 @@
         <v>0.6284289276807981</v>
       </c>
       <c r="H109">
-        <v>0.04711425206124853</v>
+        <v>0.04829210836277974</v>
       </c>
       <c r="I109">
         <v>849</v>
@@ -6286,7 +6286,7 @@
         <v>0.9480519480519335</v>
       </c>
       <c r="L109">
-        <v>0.00625</v>
+        <v>0.0125</v>
       </c>
       <c r="M109">
         <v>100</v>
@@ -6424,7 +6424,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K112">
-        <v>0.8422613854475658</v>
+        <v>0.8419399860432659</v>
       </c>
       <c r="L112">
         <v>0.03103448275862069</v>
@@ -6471,7 +6471,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K113">
-        <v>0.8155034324942791</v>
+        <v>0.815270231627109</v>
       </c>
       <c r="L113">
         <v>0.03749002924754054</v>
@@ -6782,7 +6782,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K120">
-        <v>0.8422613854475659</v>
+        <v>0.8419399860432661</v>
       </c>
       <c r="L120">
         <v>0.03103448275862069</v>
@@ -6999,7 +6999,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K125">
-        <v>0.8422613854475659</v>
+        <v>0.8419399860432663</v>
       </c>
       <c r="L125">
         <v>0.03103448275862069</v>
@@ -7125,7 +7125,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K128">
-        <v>0.8422613854475659</v>
+        <v>0.8419399860432658</v>
       </c>
       <c r="L128">
         <v>0.03103448275862069</v>
@@ -7360,7 +7360,7 @@
         <v>22.00333773087071</v>
       </c>
       <c r="K133">
-        <v>0.9622093023255821</v>
+        <v>0.9578488372093021</v>
       </c>
       <c r="L133">
         <v>0.06200527704485488</v>
@@ -7407,7 +7407,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K134">
-        <v>0.8422613854475658</v>
+        <v>0.8419399860432663</v>
       </c>
       <c r="L134">
         <v>0.03103448275862069</v>
@@ -7548,7 +7548,7 @@
         <v>22.00333773087071</v>
       </c>
       <c r="K137">
-        <v>0.9622093023255813</v>
+        <v>0.9578488372093023</v>
       </c>
       <c r="L137">
         <v>0.06200527704485488</v>
@@ -7689,7 +7689,7 @@
         <v>22.00333773087071</v>
       </c>
       <c r="K140">
-        <v>0.9622093023255816</v>
+        <v>0.9578488372093023</v>
       </c>
       <c r="L140">
         <v>0.06200527704485488</v>
@@ -7783,7 +7783,7 @@
         <v>22.00333773087071</v>
       </c>
       <c r="K142">
-        <v>0.9622093023255813</v>
+        <v>0.9578488372093023</v>
       </c>
       <c r="L142">
         <v>0.06200527704485488</v>
@@ -8053,7 +8053,7 @@
         <v>283.66</v>
       </c>
       <c r="G148">
-        <v>0.6666666666666666</v>
+        <v>0.7</v>
       </c>
       <c r="H148">
         <v>0.1428571428571428</v>
@@ -8065,7 +8065,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K148">
-        <v>0.815503432494279</v>
+        <v>0.8152702316271087</v>
       </c>
       <c r="L148">
         <v>0.03749002924754054</v>
@@ -8112,7 +8112,7 @@
         <v>13.40209830744261</v>
       </c>
       <c r="K149">
-        <v>0.8000494926998271</v>
+        <v>0.7996537224833047</v>
       </c>
       <c r="L149">
         <v>0.03686529098075585</v>
@@ -8253,7 +8253,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K152">
-        <v>0.8251108647450111</v>
+        <v>0.8248337028824834</v>
       </c>
       <c r="L152">
         <v>0.08527696793002916</v>
@@ -8391,7 +8391,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K155">
-        <v>0.8155034324942791</v>
+        <v>0.8152702316271087</v>
       </c>
       <c r="L155">
         <v>0.03749002924754054</v>
@@ -8426,7 +8426,7 @@
         <v>13655.04</v>
       </c>
       <c r="G156">
-        <v>0.5726587728740581</v>
+        <v>0.5715823466092572</v>
       </c>
       <c r="H156">
         <v>0.03979591836734694</v>
@@ -8485,7 +8485,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K157">
-        <v>0.8422613854475659</v>
+        <v>0.8419399860432663</v>
       </c>
       <c r="L157">
         <v>0.03103448275862069</v>
@@ -8802,7 +8802,7 @@
         <v>10673.57</v>
       </c>
       <c r="G164">
-        <v>0.6489493201483313</v>
+        <v>0.6477132262051916</v>
       </c>
       <c r="H164">
         <v>0.04216867469879518</v>
@@ -9002,7 +9002,7 @@
         <v>9.513810082063305</v>
       </c>
       <c r="K168">
-        <v>0.9768856447688564</v>
+        <v>0.9756690997566995</v>
       </c>
       <c r="L168">
         <v>0.0246189917936694</v>
@@ -9096,7 +9096,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K170">
-        <v>0.8155034324942803</v>
+        <v>0.8152702316271098</v>
       </c>
       <c r="L170">
         <v>0.03749002924754054</v>
@@ -9143,7 +9143,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K171">
-        <v>0.8000494926998269</v>
+        <v>0.7996537224833045</v>
       </c>
       <c r="L171">
         <v>0.03686529098075585</v>
@@ -9378,7 +9378,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K176">
-        <v>0.8155034324942791</v>
+        <v>0.815270231627109</v>
       </c>
       <c r="L176">
         <v>0.03749002924754054</v>
@@ -9425,7 +9425,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K177">
-        <v>0.8000494926998271</v>
+        <v>0.799653722483305</v>
       </c>
       <c r="L177">
         <v>0.03686529098075585</v>
@@ -9472,7 +9472,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K178">
-        <v>0.8251108647450108</v>
+        <v>0.8248337028824834</v>
       </c>
       <c r="L178">
         <v>0.08527696793002916</v>
@@ -9707,7 +9707,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K183">
-        <v>0.8422613854475655</v>
+        <v>0.8419399860432659</v>
       </c>
       <c r="L183">
         <v>0.03103448275862069</v>
@@ -9801,7 +9801,7 @@
         <v>14.18815599343186</v>
       </c>
       <c r="K185">
-        <v>0.8422613854475647</v>
+        <v>0.8419399860432651</v>
       </c>
       <c r="L185">
         <v>0.03103448275862069</v>
@@ -9848,7 +9848,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K186">
-        <v>0.8155034324942757</v>
+        <v>0.8152702316271045</v>
       </c>
       <c r="L186">
         <v>0.03749002924754054</v>
@@ -9895,7 +9895,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K187">
-        <v>0.8000494926998271</v>
+        <v>0.7996537224833057</v>
       </c>
       <c r="L187">
         <v>0.03686529098075585</v>
@@ -10130,7 +10130,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K192">
-        <v>0.8000494926998271</v>
+        <v>0.7996537224833054</v>
       </c>
       <c r="L192">
         <v>0.03686529098075585</v>
@@ -10177,7 +10177,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K193">
-        <v>0.8251108647450111</v>
+        <v>0.8248337028824834</v>
       </c>
       <c r="L193">
         <v>0.08527696793002916</v>
@@ -10412,7 +10412,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K198">
-        <v>0.8000494926998267</v>
+        <v>0.7996537224833045</v>
       </c>
       <c r="L198">
         <v>0.03686529098075585</v>
@@ -10638,7 +10638,7 @@
         <v>0.9493813273340832</v>
       </c>
       <c r="H203">
-        <v>0.04914529914529914</v>
+        <v>0.05021367521367522</v>
       </c>
       <c r="I203">
         <v>936</v>
@@ -10650,7 +10650,7 @@
         <v>0.933349609375</v>
       </c>
       <c r="L203">
-        <v>0.03635084427767354</v>
+        <v>0.03658536585365853</v>
       </c>
       <c r="M203">
         <v>41.99</v>
@@ -10741,7 +10741,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K205">
-        <v>0.8155034324942793</v>
+        <v>0.8152702316271087</v>
       </c>
       <c r="L205">
         <v>0.03749002924754054</v>
@@ -10788,7 +10788,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K206">
-        <v>0.8000494926998271</v>
+        <v>0.7996537224833006</v>
       </c>
       <c r="L206">
         <v>0.03686529098075585</v>
@@ -10835,7 +10835,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K207">
-        <v>0.8251108647450111</v>
+        <v>0.8248337028824834</v>
       </c>
       <c r="L207">
         <v>0.08527696793002916</v>
@@ -10870,7 +10870,7 @@
         <v>7947.81</v>
       </c>
       <c r="G208">
-        <v>0.5923217550274223</v>
+        <v>0.5901639344262295</v>
       </c>
       <c r="H208">
         <v>0.02586206896551724</v>
@@ -10976,7 +10976,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K210">
-        <v>0.8422613854475659</v>
+        <v>0.8419399860432659</v>
       </c>
       <c r="L210">
         <v>0.03103448275862069</v>
@@ -11023,7 +11023,7 @@
         <v>15.15827439510769</v>
       </c>
       <c r="K211">
-        <v>0.8155034324942788</v>
+        <v>0.8152702316271088</v>
       </c>
       <c r="L211">
         <v>0.03749002924754054</v>
@@ -11258,7 +11258,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K216">
-        <v>0.8155034324942787</v>
+        <v>0.8152702316271091</v>
       </c>
       <c r="L216">
         <v>0.03749002924754054</v>
@@ -11663,7 +11663,7 @@
         <v>3666.5</v>
       </c>
       <c r="G225">
-        <v>0.7549019607843137</v>
+        <v>0.7560975609756098</v>
       </c>
       <c r="H225">
         <v>0.04680851063829787</v>
@@ -11954,7 +11954,7 @@
         <v>12.24570930232558</v>
       </c>
       <c r="K231">
-        <v>0.9039156626506034</v>
+        <v>0.9033132530120485</v>
       </c>
       <c r="L231">
         <v>0.03139534883720931</v>
@@ -12048,7 +12048,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K233">
-        <v>0.8422613854475659</v>
+        <v>0.8419399860432659</v>
       </c>
       <c r="L233">
         <v>0.03103448275862069</v>
@@ -12095,7 +12095,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K234">
-        <v>0.8155034324942791</v>
+        <v>0.815270231627109</v>
       </c>
       <c r="L234">
         <v>0.03749002924754054</v>
@@ -12142,7 +12142,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K235">
-        <v>0.8251108647450106</v>
+        <v>0.8248337028824831</v>
       </c>
       <c r="L235">
         <v>0.08527696793002916</v>
@@ -12283,7 +12283,7 @@
         <v>12.24570930232558</v>
       </c>
       <c r="K238">
-        <v>0.903915662650603</v>
+        <v>0.9033132530120478</v>
       </c>
       <c r="L238">
         <v>0.03139534883720931</v>
@@ -12377,7 +12377,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K240">
-        <v>0.8155034324942791</v>
+        <v>0.815270231627109</v>
       </c>
       <c r="L240">
         <v>0.03749002924754054</v>
@@ -12424,7 +12424,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K241">
-        <v>0.8000494926998271</v>
+        <v>0.7996537224833052</v>
       </c>
       <c r="L241">
         <v>0.03686529098075585</v>
@@ -12565,7 +12565,7 @@
         <v>12.24570930232558</v>
       </c>
       <c r="K244">
-        <v>0.9039156626506024</v>
+        <v>0.9033132530120482</v>
       </c>
       <c r="L244">
         <v>0.03139534883720931</v>
@@ -12800,7 +12800,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K249">
-        <v>0.8422613854475659</v>
+        <v>0.8419399860432659</v>
       </c>
       <c r="L249">
         <v>0.03103448275862069</v>
@@ -12932,7 +12932,7 @@
         <v>0.6071428571428571</v>
       </c>
       <c r="H252">
-        <v>0.05660377358490566</v>
+        <v>0.06132075471698113</v>
       </c>
       <c r="I252">
         <v>212</v>
@@ -13129,7 +13129,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K256">
-        <v>0.8422613854475651</v>
+        <v>0.8419399860432656</v>
       </c>
       <c r="L256">
         <v>0.03103448275862069</v>
@@ -13176,7 +13176,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K257">
-        <v>0.8251108647450107</v>
+        <v>0.8248337028824833</v>
       </c>
       <c r="L257">
         <v>0.08527696793002916</v>
@@ -13408,7 +13408,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K262">
-        <v>0.8251108647450111</v>
+        <v>0.8248337028824834</v>
       </c>
       <c r="L262">
         <v>0.08527696793002916</v>
@@ -13643,7 +13643,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K267">
-        <v>0.8000494926998268</v>
+        <v>0.7996537224833045</v>
       </c>
       <c r="L267">
         <v>0.03686529098075585</v>
@@ -13690,7 +13690,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K268">
-        <v>0.8251108647450111</v>
+        <v>0.8248337028824834</v>
       </c>
       <c r="L268">
         <v>0.08527696793002916</v>
@@ -13878,7 +13878,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K272">
-        <v>0.8422613854475653</v>
+        <v>0.8419399860432658</v>
       </c>
       <c r="L272">
         <v>0.03103448275862069</v>
@@ -13925,7 +13925,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K273">
-        <v>0.8251108647450111</v>
+        <v>0.8248337028824834</v>
       </c>
       <c r="L273">
         <v>0.08527696793002916</v>
@@ -14113,7 +14113,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K277">
-        <v>0.8422613854475652</v>
+        <v>0.8419399860432657</v>
       </c>
       <c r="L277">
         <v>0.03103448275862069</v>
@@ -14157,7 +14157,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K278">
-        <v>0.8422613854475659</v>
+        <v>0.8419399860432659</v>
       </c>
       <c r="L278">
         <v>0.03103448275862069</v>
@@ -14298,7 +14298,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K281">
-        <v>0.8422613854475656</v>
+        <v>0.841939986043266</v>
       </c>
       <c r="L281">
         <v>0.03103448275862069</v>
@@ -14345,7 +14345,7 @@
         <v>7.487754232599315</v>
       </c>
       <c r="K282">
-        <v>0.9425769514200373</v>
+        <v>0.9424101575786349</v>
       </c>
       <c r="L282">
         <v>0.02550625207480358</v>
@@ -14392,7 +14392,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K283">
-        <v>0.8422613854475657</v>
+        <v>0.8419399860432661</v>
       </c>
       <c r="L283">
         <v>0.03103448275862069</v>
@@ -14771,7 +14771,7 @@
         <v>0.933751858582533</v>
       </c>
       <c r="L291">
-        <v>0.02274198769828423</v>
+        <v>0.02282292003884752</v>
       </c>
       <c r="M291">
         <v>38.91</v>
@@ -14862,7 +14862,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K293">
-        <v>0.8155034324942787</v>
+        <v>0.815270231627109</v>
       </c>
       <c r="L293">
         <v>0.03749002924754054</v>
@@ -14909,7 +14909,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K294">
-        <v>0.8000494926998271</v>
+        <v>0.7996537224833055</v>
       </c>
       <c r="L294">
         <v>0.03686529098075585</v>
@@ -14956,7 +14956,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K295">
-        <v>0.8251108647450122</v>
+        <v>0.8248337028824847</v>
       </c>
       <c r="L295">
         <v>0.08527696793002916</v>
@@ -15194,7 +15194,7 @@
         <v>0.9337518585825211</v>
       </c>
       <c r="L300">
-        <v>0.02274198769828423</v>
+        <v>0.02282292003884752</v>
       </c>
       <c r="M300">
         <v>1.93</v>
@@ -15226,7 +15226,7 @@
         <v>276.34</v>
       </c>
       <c r="G301">
-        <v>0.6</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="H301">
         <v>0.1818181818181818</v>
@@ -15285,7 +15285,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K302">
-        <v>0.8000494926998268</v>
+        <v>0.7996537224833045</v>
       </c>
       <c r="L302">
         <v>0.03686529098075585</v>
@@ -15332,7 +15332,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K303">
-        <v>0.8251108647450106</v>
+        <v>0.8248337028824831</v>
       </c>
       <c r="L303">
         <v>0.08527696793002916</v>
@@ -15614,7 +15614,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K309">
-        <v>0.8000494926998267</v>
+        <v>0.7996537224833045</v>
       </c>
       <c r="L309">
         <v>0.03686529098075585</v>
@@ -15758,7 +15758,7 @@
         <v>0.9337518585825402</v>
       </c>
       <c r="L312">
-        <v>0.02274198769828423</v>
+        <v>0.02282292003884752</v>
       </c>
       <c r="M312">
         <v>34.24</v>
@@ -15837,10 +15837,10 @@
         <v>796.51</v>
       </c>
       <c r="G314">
-        <v>0.5473684210526316</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="H314">
-        <v>0.0202020202020202</v>
+        <v>0.0303030303030303</v>
       </c>
       <c r="I314">
         <v>99</v>
@@ -15849,7 +15849,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K314">
-        <v>0.8422613854475663</v>
+        <v>0.8419399860432667</v>
       </c>
       <c r="L314">
         <v>0.03103448275862069</v>
@@ -16225,7 +16225,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K322">
-        <v>0.8155034324942791</v>
+        <v>0.815270231627109</v>
       </c>
       <c r="L322">
         <v>0.03749002924754054</v>
@@ -16319,7 +16319,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K324">
-        <v>0.8422613854475659</v>
+        <v>0.841939986043266</v>
       </c>
       <c r="L324">
         <v>0.03103448275862069</v>
@@ -16583,7 +16583,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K330">
-        <v>0.8422613854475656</v>
+        <v>0.841939986043266</v>
       </c>
       <c r="L330">
         <v>0.03103448275862069</v>
@@ -16630,7 +16630,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K331">
-        <v>0.8155034324942789</v>
+        <v>0.8152702316271087</v>
       </c>
       <c r="L331">
         <v>0.03749002924754054</v>
@@ -16724,7 +16724,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K333">
-        <v>0.8155034324942791</v>
+        <v>0.815270231627109</v>
       </c>
       <c r="L333">
         <v>0.03749002924754054</v>
@@ -16929,7 +16929,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K338">
-        <v>0.8422613854475655</v>
+        <v>0.8419399860432659</v>
       </c>
       <c r="L338">
         <v>0.03103448275862069</v>
@@ -16976,7 +16976,7 @@
         <v>15.15827439510769</v>
       </c>
       <c r="K339">
-        <v>0.81550343249428</v>
+        <v>0.8152702316271098</v>
       </c>
       <c r="L339">
         <v>0.03749002924754054</v>
@@ -17381,7 +17381,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K348">
-        <v>0.8422613854475678</v>
+        <v>0.8419399860432683</v>
       </c>
       <c r="L348">
         <v>0.03103448275862069</v>
@@ -17492,7 +17492,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K351">
-        <v>0.8155034324942786</v>
+        <v>0.8152702316271094</v>
       </c>
       <c r="L351">
         <v>0.03749002924754054</v>
@@ -17539,7 +17539,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K352">
-        <v>0.8251108647450118</v>
+        <v>0.8248337028824844</v>
       </c>
       <c r="L352">
         <v>0.08527696793002916</v>
@@ -17682,7 +17682,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K356">
-        <v>0.8422613854475671</v>
+        <v>0.8419399860432676</v>
       </c>
       <c r="L356">
         <v>0.03103448275862069</v>
@@ -17729,7 +17729,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K357">
-        <v>0.8155034324942809</v>
+        <v>0.81527023162711</v>
       </c>
       <c r="L357">
         <v>0.03749002924754054</v>
@@ -17776,7 +17776,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K358">
-        <v>0.8251108647450128</v>
+        <v>0.8248337028824854</v>
       </c>
       <c r="L358">
         <v>0.08527696793002916</v>
@@ -17951,7 +17951,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K363">
-        <v>0.8422613854475659</v>
+        <v>0.8419399860432658</v>
       </c>
       <c r="L363">
         <v>0.03103448275862069</v>
@@ -17986,7 +17986,7 @@
         <v>4344.3</v>
       </c>
       <c r="G364">
-        <v>0.956268221574344</v>
+        <v>0.9563953488372093</v>
       </c>
       <c r="H364">
         <v>0.08616187989556136</v>
@@ -17998,7 +17998,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K364">
-        <v>0.815503432494273</v>
+        <v>0.8152702316271019</v>
       </c>
       <c r="L364">
         <v>0.03749002924754054</v>
@@ -18045,7 +18045,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K365">
-        <v>0.8251108647450118</v>
+        <v>0.8248337028824844</v>
       </c>
       <c r="L365">
         <v>0.08527696793002916</v>
@@ -18124,7 +18124,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K367">
-        <v>0.8155034324942791</v>
+        <v>0.815270231627109</v>
       </c>
       <c r="L367">
         <v>0.03749002924754054</v>
@@ -18265,7 +18265,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K370">
-        <v>0.8422613854475649</v>
+        <v>0.8419399860432654</v>
       </c>
       <c r="L370">
         <v>0.03103448275862069</v>
@@ -18312,7 +18312,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K371">
-        <v>0.8155034324942786</v>
+        <v>0.8152702316271092</v>
       </c>
       <c r="L371">
         <v>0.03749002924754054</v>
@@ -18532,7 +18532,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K376">
-        <v>0.8422613854475659</v>
+        <v>0.8419399860432658</v>
       </c>
       <c r="L376">
         <v>0.03103448275862069</v>
@@ -18579,7 +18579,7 @@
         <v>15.15827439510769</v>
       </c>
       <c r="K377">
-        <v>0.8155034324942748</v>
+        <v>0.8152702316271037</v>
       </c>
       <c r="L377">
         <v>0.03749002924754054</v>
@@ -18626,7 +18626,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K378">
-        <v>0.8422613854475658</v>
+        <v>0.8419399860432659</v>
       </c>
       <c r="L378">
         <v>0.03103448275862069</v>
@@ -18673,7 +18673,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K379">
-        <v>0.8422613854475659</v>
+        <v>0.841939986043266</v>
       </c>
       <c r="L379">
         <v>0.03103448275862069</v>
@@ -18767,7 +18767,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K381">
-        <v>0.8155034324942791</v>
+        <v>0.815270231627109</v>
       </c>
       <c r="L381">
         <v>0.03749002924754054</v>
@@ -18814,7 +18814,7 @@
         <v>11.30720848056537</v>
       </c>
       <c r="K382">
-        <v>0.7920000000000003</v>
+        <v>0.7888446215139443</v>
       </c>
       <c r="L382">
         <v>0.06007067137809187</v>
@@ -18955,7 +18955,7 @@
         <v>11.30720848056537</v>
       </c>
       <c r="K385">
-        <v>0.7920000000000013</v>
+        <v>0.7888446215139432</v>
       </c>
       <c r="L385">
         <v>0.06007067137809186</v>
@@ -19096,7 +19096,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K388">
-        <v>0.8155034324942786</v>
+        <v>0.8152702316271092</v>
       </c>
       <c r="L388">
         <v>0.03749002924754054</v>
@@ -19143,7 +19143,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K389">
-        <v>0.8000494926998271</v>
+        <v>0.7996537224833028</v>
       </c>
       <c r="L389">
         <v>0.03686529098075585</v>
@@ -19190,7 +19190,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K390">
-        <v>0.8251108647450113</v>
+        <v>0.8248337028824838</v>
       </c>
       <c r="L390">
         <v>0.08527696793002917</v>
@@ -19237,7 +19237,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K391">
-        <v>0.8422613854475658</v>
+        <v>0.8419399860432663</v>
       </c>
       <c r="L391">
         <v>0.03103448275862069</v>
@@ -19284,7 +19284,7 @@
         <v>11.30720848056537</v>
       </c>
       <c r="K392">
-        <v>0.7919999999999999</v>
+        <v>0.7888446215139443</v>
       </c>
       <c r="L392">
         <v>0.06007067137809187</v>
@@ -19331,7 +19331,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K393">
-        <v>0.8000494926998267</v>
+        <v>0.7996537224833045</v>
       </c>
       <c r="L393">
         <v>0.03686529098075585</v>
@@ -19519,7 +19519,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K397">
-        <v>0.8422613854475659</v>
+        <v>0.8419399860432658</v>
       </c>
       <c r="L397">
         <v>0.03103448275862069</v>
@@ -19566,7 +19566,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K398">
-        <v>0.8155034324942791</v>
+        <v>0.815270231627109</v>
       </c>
       <c r="L398">
         <v>0.03749002924754054</v>
@@ -19754,7 +19754,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K402">
-        <v>0.8155034324942798</v>
+        <v>0.8152702316271098</v>
       </c>
       <c r="L402">
         <v>0.03749002924754054</v>
@@ -20036,7 +20036,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K408">
-        <v>0.8422613854475661</v>
+        <v>0.8419399860432666</v>
       </c>
       <c r="L408">
         <v>0.03103448275862069</v>
@@ -20271,7 +20271,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K413">
-        <v>0.8422613854475671</v>
+        <v>0.8419399860432676</v>
       </c>
       <c r="L413">
         <v>0.03103448275862069</v>
@@ -20506,7 +20506,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K418">
-        <v>0.8422613854475653</v>
+        <v>0.8419399860432658</v>
       </c>
       <c r="L418">
         <v>0.03103448275862069</v>
@@ -20553,7 +20553,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K419">
-        <v>0.8155034324942806</v>
+        <v>0.8152702316271099</v>
       </c>
       <c r="L419">
         <v>0.03749002924754054</v>
@@ -20600,7 +20600,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K420">
-        <v>0.8000494926998271</v>
+        <v>0.7996537224833019</v>
       </c>
       <c r="L420">
         <v>0.03686529098075585</v>
@@ -20788,7 +20788,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K424">
-        <v>0.8422613854475659</v>
+        <v>0.841939986043266</v>
       </c>
       <c r="L424">
         <v>0.03103448275862069</v>
@@ -20835,7 +20835,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K425">
-        <v>0.8155034324942808</v>
+        <v>0.81527023162711</v>
       </c>
       <c r="L425">
         <v>0.03749002924754054</v>
@@ -20882,7 +20882,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K426">
-        <v>0.8000494926998271</v>
+        <v>0.7996537224833055</v>
       </c>
       <c r="L426">
         <v>0.03686529098075585</v>
@@ -20929,7 +20929,7 @@
         <v>13.0609961127308</v>
       </c>
       <c r="K427">
-        <v>0.8251108647450105</v>
+        <v>0.824833702882483</v>
       </c>
       <c r="L427">
         <v>0.08527696793002916</v>
@@ -21164,7 +21164,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K432">
-        <v>0.8422613854475659</v>
+        <v>0.841939986043266</v>
       </c>
       <c r="L432">
         <v>0.03103448275862069</v>
@@ -21211,7 +21211,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K433">
-        <v>0.8155034324942769</v>
+        <v>0.8152702316271059</v>
       </c>
       <c r="L433">
         <v>0.03749002924754054</v>
@@ -21258,7 +21258,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K434">
-        <v>0.8000494926998271</v>
+        <v>0.7996537224833007</v>
       </c>
       <c r="L434">
         <v>0.03686529098075585</v>
@@ -21305,7 +21305,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K435">
-        <v>0.8251108647450046</v>
+        <v>0.8248337028824771</v>
       </c>
       <c r="L435">
         <v>0.08527696793002916</v>
@@ -21399,7 +21399,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K437">
-        <v>0.8155034324942809</v>
+        <v>0.81527023162711</v>
       </c>
       <c r="L437">
         <v>0.03749002924754054</v>
@@ -21493,7 +21493,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K439">
-        <v>0.8422613854475658</v>
+        <v>0.8419399860432661</v>
       </c>
       <c r="L439">
         <v>0.03103448275862069</v>
@@ -21540,7 +21540,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K440">
-        <v>0.8155034324942791</v>
+        <v>0.8152702316271089</v>
       </c>
       <c r="L440">
         <v>0.03749002924754054</v>
@@ -21760,7 +21760,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K445">
-        <v>0.8422613854475649</v>
+        <v>0.8419399860432653</v>
       </c>
       <c r="L445">
         <v>0.03103448275862069</v>
@@ -21807,7 +21807,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K446">
-        <v>0.8155034324942788</v>
+        <v>0.8152702316271087</v>
       </c>
       <c r="L446">
         <v>0.03749002924754054</v>
@@ -21901,7 +21901,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K448">
-        <v>0.8422613854475659</v>
+        <v>0.841939986043266</v>
       </c>
       <c r="L448">
         <v>0.03103448275862069</v>
@@ -22136,7 +22136,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K453">
-        <v>0.8422613854475659</v>
+        <v>0.8419399860432659</v>
       </c>
       <c r="L453">
         <v>0.03103448275862069</v>
@@ -22371,7 +22371,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K458">
-        <v>0.8422613854475658</v>
+        <v>0.8419399860432659</v>
       </c>
       <c r="L458">
         <v>0.03103448275862069</v>
@@ -22462,7 +22462,7 @@
         <v>15.15827439510769</v>
       </c>
       <c r="K460">
-        <v>0.8155034324942791</v>
+        <v>0.8152702316271089</v>
       </c>
       <c r="L460">
         <v>0.03749002924754054</v>
@@ -22509,7 +22509,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K461">
-        <v>0.8251108647450111</v>
+        <v>0.8248337028824835</v>
       </c>
       <c r="L461">
         <v>0.08527696793002916</v>
@@ -22556,7 +22556,7 @@
         <v>16.50988888888889</v>
       </c>
       <c r="K462">
-        <v>0.6202531645569624</v>
+        <v>0.6218487394957986</v>
       </c>
       <c r="L462">
         <v>0.07037037037037037</v>
@@ -22729,7 +22729,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K466">
-        <v>0.8155034324942787</v>
+        <v>0.815270231627109</v>
       </c>
       <c r="L466">
         <v>0.03749002924754054</v>
@@ -22776,7 +22776,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K467">
-        <v>0.8000494926998271</v>
+        <v>0.799653722483305</v>
       </c>
       <c r="L467">
         <v>0.03686529098075585</v>
@@ -22823,7 +22823,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K468">
-        <v>0.8251108647450112</v>
+        <v>0.8248337028824837</v>
       </c>
       <c r="L468">
         <v>0.08527696793002916</v>
@@ -22870,7 +22870,7 @@
         <v>16.50988888888889</v>
       </c>
       <c r="K469">
-        <v>0.6202531645569619</v>
+        <v>0.6218487394957981</v>
       </c>
       <c r="L469">
         <v>0.07037037037037037</v>
@@ -22917,7 +22917,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K470">
-        <v>0.8422613854475659</v>
+        <v>0.8419399860432658</v>
       </c>
       <c r="L470">
         <v>0.03103448275862069</v>
@@ -23028,7 +23028,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K473">
-        <v>0.8422613854475659</v>
+        <v>0.8419399860432661</v>
       </c>
       <c r="L473">
         <v>0.03103448275862069</v>
@@ -23075,7 +23075,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K474">
-        <v>0.8155034324942791</v>
+        <v>0.815270231627109</v>
       </c>
       <c r="L474">
         <v>0.03749002924754054</v>
@@ -23122,7 +23122,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K475">
-        <v>0.8251108647450108</v>
+        <v>0.8248337028824834</v>
       </c>
       <c r="L475">
         <v>0.08527696793002916</v>
@@ -23297,7 +23297,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K480">
-        <v>0.8422613854475652</v>
+        <v>0.8419399860432656</v>
       </c>
       <c r="L480">
         <v>0.03103448275862069</v>
@@ -23344,7 +23344,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K481">
-        <v>0.815503432494279</v>
+        <v>0.8152702316271095</v>
       </c>
       <c r="L481">
         <v>0.03749002924754054</v>
@@ -23391,7 +23391,7 @@
         <v>13.40209830744261</v>
       </c>
       <c r="K482">
-        <v>0.8000494926998269</v>
+        <v>0.7996537224833058</v>
       </c>
       <c r="L482">
         <v>0.03686529098075585</v>
@@ -23438,7 +23438,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K483">
-        <v>0.8251108647450115</v>
+        <v>0.824833702882484</v>
       </c>
       <c r="L483">
         <v>0.08527696793002916</v>
@@ -23485,7 +23485,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K484">
-        <v>0.8155034324942791</v>
+        <v>0.815270231627109</v>
       </c>
       <c r="L484">
         <v>0.03749002924754054</v>
@@ -23532,7 +23532,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K485">
-        <v>0.8422613854475659</v>
+        <v>0.841939986043266</v>
       </c>
       <c r="L485">
         <v>0.03103448275862069</v>
@@ -23814,7 +23814,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K491">
-        <v>0.8422613854475651</v>
+        <v>0.8419399860432656</v>
       </c>
       <c r="L491">
         <v>0.03103448275862069</v>
@@ -23955,7 +23955,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K494">
-        <v>0.8422613854475659</v>
+        <v>0.8419399860432661</v>
       </c>
       <c r="L494">
         <v>0.03103448275862069</v>
@@ -24049,7 +24049,7 @@
         <v>15.15827439510769</v>
       </c>
       <c r="K496">
-        <v>0.8155034324942787</v>
+        <v>0.815270231627109</v>
       </c>
       <c r="L496">
         <v>0.03749002924754054</v>
@@ -24096,7 +24096,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K497">
-        <v>0.8000494926998268</v>
+        <v>0.7996537224833045</v>
       </c>
       <c r="L497">
         <v>0.03686529098075585</v>
@@ -24140,7 +24140,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K498">
-        <v>0.8251108647450111</v>
+        <v>0.8248337028824834</v>
       </c>
       <c r="L498">
         <v>0.08527696793002916</v>
@@ -24328,7 +24328,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K502">
-        <v>0.8422613854475653</v>
+        <v>0.8419399860432658</v>
       </c>
       <c r="L502">
         <v>0.03103448275862069</v>
@@ -24375,7 +24375,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K503">
-        <v>0.8155034324942803</v>
+        <v>0.8152702316271098</v>
       </c>
       <c r="L503">
         <v>0.03749002924754054</v>
@@ -24422,7 +24422,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K504">
-        <v>0.8000494926998271</v>
+        <v>0.7996537224833052</v>
       </c>
       <c r="L504">
         <v>0.03686529098075585</v>
@@ -24469,7 +24469,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K505">
-        <v>0.8251108647450106</v>
+        <v>0.8248337028824831</v>
       </c>
       <c r="L505">
         <v>0.08527696793002916</v>
@@ -24657,7 +24657,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K509">
-        <v>0.8422613854475659</v>
+        <v>0.841939986043266</v>
       </c>
       <c r="L509">
         <v>0.03103448275862069</v>
@@ -24751,7 +24751,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K511">
-        <v>0.8155034324942764</v>
+        <v>0.8152702316271052</v>
       </c>
       <c r="L511">
         <v>0.03749002924754054</v>
@@ -24798,7 +24798,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K512">
-        <v>0.8000494926998271</v>
+        <v>0.7996537224833016</v>
       </c>
       <c r="L512">
         <v>0.03686529098075585</v>
@@ -24845,7 +24845,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K513">
-        <v>0.8251108647450128</v>
+        <v>0.8248337028824854</v>
       </c>
       <c r="L513">
         <v>0.08527696793002916</v>
@@ -24936,7 +24936,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K515">
-        <v>0.8155034324942791</v>
+        <v>0.815270231627109</v>
       </c>
       <c r="L515">
         <v>0.03749002924754054</v>
@@ -24983,7 +24983,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K516">
-        <v>0.8000494926998267</v>
+        <v>0.7996537224833045</v>
       </c>
       <c r="L516">
         <v>0.03686529098075585</v>
@@ -25077,7 +25077,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K518">
-        <v>0.8422613854475656</v>
+        <v>0.8419399860432661</v>
       </c>
       <c r="L518">
         <v>0.03103448275862069</v>
@@ -25124,7 +25124,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K519">
-        <v>0.8155034324942837</v>
+        <v>0.8152702316270989</v>
       </c>
       <c r="L519">
         <v>0.03749002924754054</v>
@@ -25171,7 +25171,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K520">
-        <v>0.8000494926998271</v>
+        <v>0.7996537224833019</v>
       </c>
       <c r="L520">
         <v>0.03686529098075585</v>
@@ -25221,7 +25221,7 @@
         <v>0.8821596244131464</v>
       </c>
       <c r="L521">
-        <v>0.0657030223390276</v>
+        <v>0.06614104248795445</v>
       </c>
       <c r="M521">
         <v>34.1</v>
@@ -25265,7 +25265,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K522">
-        <v>0.8000494926998271</v>
+        <v>0.7996537224833039</v>
       </c>
       <c r="L522">
         <v>0.03686529098075585</v>
@@ -25312,7 +25312,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K523">
-        <v>0.8251108647450111</v>
+        <v>0.8248337028824834</v>
       </c>
       <c r="L523">
         <v>0.08527696793002916</v>
@@ -25500,7 +25500,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K527">
-        <v>0.8155034324942795</v>
+        <v>0.8152702316271097</v>
       </c>
       <c r="L527">
         <v>0.03749002924754054</v>
@@ -25547,7 +25547,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K528">
-        <v>0.8000494926998271</v>
+        <v>0.7996537224833026</v>
       </c>
       <c r="L528">
         <v>0.03686529098075585</v>
@@ -25594,7 +25594,7 @@
         <v>13.0609961127308</v>
       </c>
       <c r="K529">
-        <v>0.8251108647450106</v>
+        <v>0.8248337028824831</v>
       </c>
       <c r="L529">
         <v>0.08527696793002916</v>
@@ -25782,7 +25782,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K533">
-        <v>0.8155034324942786</v>
+        <v>0.8152702316271093</v>
       </c>
       <c r="L533">
         <v>0.03749002924754054</v>
@@ -25829,7 +25829,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K534">
-        <v>0.8000494926998271</v>
+        <v>0.7996537224833014</v>
       </c>
       <c r="L534">
         <v>0.03686529098075585</v>
@@ -25876,7 +25876,7 @@
         <v>13.0609961127308</v>
       </c>
       <c r="K535">
-        <v>0.8251108647450106</v>
+        <v>0.8248337028824831</v>
       </c>
       <c r="L535">
         <v>0.08527696793002916</v>
@@ -25923,7 +25923,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K536">
-        <v>0.8000494926998271</v>
+        <v>0.7996537224832998</v>
       </c>
       <c r="L536">
         <v>0.03686529098075585</v>
@@ -25973,7 +25973,7 @@
         <v>0.8821596244131457</v>
       </c>
       <c r="L537">
-        <v>0.0657030223390276</v>
+        <v>0.06614104248795445</v>
       </c>
       <c r="M537">
         <v>1.25</v>
@@ -26017,7 +26017,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K538">
-        <v>0.8000494926998271</v>
+        <v>0.7996537224833001</v>
       </c>
       <c r="L538">
         <v>0.03686529098075585</v>
@@ -26284,7 +26284,7 @@
         <v>14.18815599343186</v>
       </c>
       <c r="K544">
-        <v>0.8422613854475649</v>
+        <v>0.8419399860432654</v>
       </c>
       <c r="L544">
         <v>0.03103448275862069</v>
@@ -26331,7 +26331,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K545">
-        <v>0.8155034324942786</v>
+        <v>0.8152702316271094</v>
       </c>
       <c r="L545">
         <v>0.03749002924754054</v>
@@ -26795,7 +26795,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K555">
-        <v>0.8422613854475659</v>
+        <v>0.8419399860432658</v>
       </c>
       <c r="L555">
         <v>0.03103448275862069</v>
@@ -26839,7 +26839,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K556">
-        <v>0.8155034324942791</v>
+        <v>0.815270231627109</v>
       </c>
       <c r="L556">
         <v>0.03749002924754054</v>
@@ -26886,7 +26886,7 @@
         <v>13.40209830744261</v>
       </c>
       <c r="K557">
-        <v>0.8000494926998271</v>
+        <v>0.7996537224833054</v>
       </c>
       <c r="L557">
         <v>0.03686529098075585</v>
@@ -27074,7 +27074,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K561">
-        <v>0.8422613854475648</v>
+        <v>0.8419399860432653</v>
       </c>
       <c r="L561">
         <v>0.03103448275862069</v>
@@ -27121,7 +27121,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K562">
-        <v>0.8155034324942786</v>
+        <v>0.8152702316271094</v>
       </c>
       <c r="L562">
         <v>0.03749002924754054</v>
@@ -27168,7 +27168,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K563">
-        <v>0.8251108647450105</v>
+        <v>0.824833702882483</v>
       </c>
       <c r="L563">
         <v>0.08527696793002916</v>
@@ -27250,7 +27250,7 @@
         <v>8506.92</v>
       </c>
       <c r="G565">
-        <v>0.8771626297577855</v>
+        <v>0.8754325259515571</v>
       </c>
       <c r="H565">
         <v>0.0302013422818792</v>
@@ -27403,7 +27403,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K568">
-        <v>0.8422613854475666</v>
+        <v>0.841939986043267</v>
       </c>
       <c r="L568">
         <v>0.03103448275862069</v>
@@ -27450,7 +27450,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K569">
-        <v>0.8155034324942739</v>
+        <v>0.8152702316271028</v>
       </c>
       <c r="L569">
         <v>0.03749002924754054</v>
@@ -27485,7 +27485,7 @@
         <v>5763.78</v>
       </c>
       <c r="G570">
-        <v>0.8671497584541062</v>
+        <v>0.8647342995169082</v>
       </c>
       <c r="H570">
         <v>0.02564102564102564</v>
@@ -27497,7 +27497,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K570">
-        <v>0.8000494926998271</v>
+        <v>0.7996537224833005</v>
       </c>
       <c r="L570">
         <v>0.03686529098075585</v>
@@ -27544,7 +27544,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K571">
-        <v>0.8251108647450111</v>
+        <v>0.8248337028824834</v>
       </c>
       <c r="L571">
         <v>0.08527696793002916</v>
@@ -27591,7 +27591,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K572">
-        <v>0.8251108647450111</v>
+        <v>0.8248337028824834</v>
       </c>
       <c r="L572">
         <v>0.08527696793002916</v>
@@ -27641,7 +27641,7 @@
         <v>0.6135458167330679</v>
       </c>
       <c r="L573">
-        <v>0.04751735184196477</v>
+        <v>0.04805125467164975</v>
       </c>
       <c r="M573">
         <v>57.89</v>
@@ -27685,7 +27685,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K574">
-        <v>0.8422613854475659</v>
+        <v>0.8419399860432658</v>
       </c>
       <c r="L574">
         <v>0.03103448275862069</v>
@@ -27732,7 +27732,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K575">
-        <v>0.8251108647450111</v>
+        <v>0.8248337028824834</v>
       </c>
       <c r="L575">
         <v>0.08527696793002916</v>
@@ -27782,7 +27782,7 @@
         <v>0.6135458167330677</v>
       </c>
       <c r="L576">
-        <v>0.04751735184196476</v>
+        <v>0.04805125467164976</v>
       </c>
       <c r="M576">
         <v>32.65</v>
@@ -27920,7 +27920,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K579">
-        <v>0.8422613854475659</v>
+        <v>0.8419399860432659</v>
       </c>
       <c r="L579">
         <v>0.03103448275862069</v>
@@ -27967,7 +27967,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K580">
-        <v>0.8000494926998271</v>
+        <v>0.7996537224833045</v>
       </c>
       <c r="L580">
         <v>0.03686529098075585</v>
@@ -28014,7 +28014,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K581">
-        <v>0.8251108647450109</v>
+        <v>0.8248337028824835</v>
       </c>
       <c r="L581">
         <v>0.08527696793002916</v>
@@ -28064,7 +28064,7 @@
         <v>0.6135458167330675</v>
       </c>
       <c r="L582">
-        <v>0.04751735184196476</v>
+        <v>0.04805125467164976</v>
       </c>
       <c r="M582">
         <v>22.13</v>
@@ -28249,7 +28249,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K586">
-        <v>0.8422613854475659</v>
+        <v>0.8419399860432659</v>
       </c>
       <c r="L586">
         <v>0.03103448275862069</v>
@@ -28296,7 +28296,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K587">
-        <v>0.8000494926998268</v>
+        <v>0.7996537224833045</v>
       </c>
       <c r="L587">
         <v>0.03686529098075585</v>
@@ -28343,7 +28343,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K588">
-        <v>0.8251108647450105</v>
+        <v>0.824833702882483</v>
       </c>
       <c r="L588">
         <v>0.08527696793002916</v>
@@ -28393,7 +28393,7 @@
         <v>0.6135458167330676</v>
       </c>
       <c r="L589">
-        <v>0.04751735184196476</v>
+        <v>0.04805125467164976</v>
       </c>
       <c r="M589">
         <v>95</v>
@@ -28437,7 +28437,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K590">
-        <v>0.8000494926998267</v>
+        <v>0.7996537224833045</v>
       </c>
       <c r="L590">
         <v>0.03686529098075585</v>
@@ -28578,7 +28578,7 @@
         <v>14.18815599343186</v>
       </c>
       <c r="K593">
-        <v>0.8422613854475662</v>
+        <v>0.8419399860432666</v>
       </c>
       <c r="L593">
         <v>0.03103448275862069</v>
@@ -28748,7 +28748,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K597">
-        <v>0.8422613854475678</v>
+        <v>0.8419399860432684</v>
       </c>
       <c r="L597">
         <v>0.03103448275862069</v>
@@ -28842,7 +28842,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K599">
-        <v>0.842261385447565</v>
+        <v>0.8419399860432654</v>
       </c>
       <c r="L599">
         <v>0.03103448275862069</v>
@@ -29124,7 +29124,7 @@
         <v>17.87864406779661</v>
       </c>
       <c r="K605">
-        <v>0.9022222222222217</v>
+        <v>0.8982300884955742</v>
       </c>
       <c r="L605">
         <v>0.03813559322033899</v>
@@ -29218,10 +29218,10 @@
         <v>7.803655068078669</v>
       </c>
       <c r="K607">
-        <v>0.7123588456712673</v>
+        <v>0.7122471381527364</v>
       </c>
       <c r="L607">
-        <v>0.03963691376701967</v>
+        <v>0.03978819969742814</v>
       </c>
       <c r="M607">
         <v>1.12</v>
@@ -29265,7 +29265,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K608">
-        <v>0.8422613854475651</v>
+        <v>0.8419399860432655</v>
       </c>
       <c r="L608">
         <v>0.03103448275862069</v>
@@ -29406,7 +29406,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K611">
-        <v>0.8155034324942788</v>
+        <v>0.8152702316271087</v>
       </c>
       <c r="L611">
         <v>0.03749002924754054</v>
@@ -29453,7 +29453,7 @@
         <v>13.40209830744261</v>
       </c>
       <c r="K612">
-        <v>0.8000494926998269</v>
+        <v>0.7996537224833024</v>
       </c>
       <c r="L612">
         <v>0.03686529098075585</v>
@@ -29500,7 +29500,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K613">
-        <v>0.8251108647450125</v>
+        <v>0.824833702882485</v>
       </c>
       <c r="L613">
         <v>0.08527696793002916</v>
@@ -29641,7 +29641,7 @@
         <v>17.87864406779661</v>
       </c>
       <c r="K616">
-        <v>0.9022222222222254</v>
+        <v>0.8982300884955781</v>
       </c>
       <c r="L616">
         <v>0.03813559322033899</v>
@@ -29735,10 +29735,10 @@
         <v>7.803655068078669</v>
       </c>
       <c r="K618">
-        <v>0.7123588456712679</v>
+        <v>0.7122471381527361</v>
       </c>
       <c r="L618">
-        <v>0.03963691376701967</v>
+        <v>0.03978819969742814</v>
       </c>
       <c r="M618">
         <v>5.43</v>
@@ -29782,7 +29782,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K619">
-        <v>0.8155034324942794</v>
+        <v>0.8152702316271097</v>
       </c>
       <c r="L619">
         <v>0.03749002924754054</v>
@@ -29829,7 +29829,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K620">
-        <v>0.8000494926998271</v>
+        <v>0.7996537224833019</v>
       </c>
       <c r="L620">
         <v>0.03686529098075585</v>
@@ -29876,7 +29876,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K621">
-        <v>0.8251108647450081</v>
+        <v>0.8248337028824806</v>
       </c>
       <c r="L621">
         <v>0.08527696793002916</v>
@@ -30017,7 +30017,7 @@
         <v>17.87864406779661</v>
       </c>
       <c r="K624">
-        <v>0.9022222222222298</v>
+        <v>0.8982300884955732</v>
       </c>
       <c r="L624">
         <v>0.03813559322033899</v>
@@ -30111,10 +30111,10 @@
         <v>7.803655068078668</v>
       </c>
       <c r="K626">
-        <v>0.7123588456712677</v>
+        <v>0.7122471381527368</v>
       </c>
       <c r="L626">
-        <v>0.03963691376701967</v>
+        <v>0.03978819969742814</v>
       </c>
       <c r="M626">
         <v>1.58</v>
@@ -30158,7 +30158,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K627">
-        <v>0.8422613854475652</v>
+        <v>0.8419399860432657</v>
       </c>
       <c r="L627">
         <v>0.03103448275862069</v>
@@ -30205,7 +30205,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K628">
-        <v>0.815503432494279</v>
+        <v>0.8152702316271087</v>
       </c>
       <c r="L628">
         <v>0.03749002924754054</v>
@@ -30252,7 +30252,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K629">
-        <v>0.8000494926998269</v>
+        <v>0.7996537224833024</v>
       </c>
       <c r="L629">
         <v>0.03686529098075585</v>
@@ -30299,7 +30299,7 @@
         <v>13.06099611273081</v>
       </c>
       <c r="K630">
-        <v>0.8251108647450054</v>
+        <v>0.8248337028824779</v>
       </c>
       <c r="L630">
         <v>0.08527696793002916</v>
@@ -30440,7 +30440,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K633">
-        <v>0.8422613854475652</v>
+        <v>0.8419399860432657</v>
       </c>
       <c r="L633">
         <v>0.03103448275862069</v>
@@ -30581,7 +30581,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K636">
-        <v>0.8155034324942787</v>
+        <v>0.8152702316271091</v>
       </c>
       <c r="L636">
         <v>0.03749002924754054</v>
@@ -30628,7 +30628,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K637">
-        <v>0.8000494926998269</v>
+        <v>0.7996537224833045</v>
       </c>
       <c r="L637">
         <v>0.03686529098075585</v>
@@ -30722,7 +30722,7 @@
         <v>17.87864406779661</v>
       </c>
       <c r="K639">
-        <v>0.9022222222222221</v>
+        <v>0.8982300884955752</v>
       </c>
       <c r="L639">
         <v>0.03813559322033899</v>
@@ -30769,7 +30769,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K640">
-        <v>0.8422613854475655</v>
+        <v>0.8419399860432659</v>
       </c>
       <c r="L640">
         <v>0.03103448275862069</v>
@@ -30910,7 +30910,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K643">
-        <v>0.8155034324942796</v>
+        <v>0.8152702316271097</v>
       </c>
       <c r="L643">
         <v>0.03749002924754054</v>
@@ -30957,7 +30957,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K644">
-        <v>0.8000494926998269</v>
+        <v>0.7996537224833054</v>
       </c>
       <c r="L644">
         <v>0.03686529098075585</v>
@@ -31239,7 +31239,7 @@
         <v>14.18815599343185</v>
       </c>
       <c r="K650">
-        <v>0.8422613854475658</v>
+        <v>0.8419399860432663</v>
       </c>
       <c r="L650">
         <v>0.03103448275862069</v>
@@ -31286,7 +31286,7 @@
         <v>15.15827439510768</v>
       </c>
       <c r="K651">
-        <v>0.815503432494279</v>
+        <v>0.8152702316271087</v>
       </c>
       <c r="L651">
         <v>0.03749002924754054</v>
@@ -31333,7 +31333,7 @@
         <v>13.40209830744262</v>
       </c>
       <c r="K652">
-        <v>0.8000494926998271</v>
+        <v>0.7996537224833045</v>
       </c>
       <c r="L652">
         <v>0.03686529098075585</v>
@@ -32310,7 +32310,7 @@
         <v>0.6135458167330688</v>
       </c>
       <c r="L674">
-        <v>0.04751735184196476</v>
+        <v>0.04805125467164976</v>
       </c>
       <c r="M674">
         <v>4.64</v>
@@ -33608,7 +33608,7 @@
         <v>0.938010393466965</v>
       </c>
       <c r="L702">
-        <v>0.03348937702556716</v>
+        <v>0.03384947785379906</v>
       </c>
       <c r="M702">
         <v>2.42</v>
@@ -33843,7 +33843,7 @@
         <v>0.9480519480519477</v>
       </c>
       <c r="L707">
-        <v>0.00625</v>
+        <v>0.0125</v>
       </c>
       <c r="M707">
         <v>0.52</v>
@@ -34242,7 +34242,7 @@
         <v>22.00333773087071</v>
       </c>
       <c r="K716">
-        <v>0.9622093023255814</v>
+        <v>0.9578488372093025</v>
       </c>
       <c r="L716">
         <v>0.06200527704485489</v>
@@ -35511,7 +35511,7 @@
         <v>7.487754232599315</v>
       </c>
       <c r="K743">
-        <v>0.9425769514199933</v>
+        <v>0.942410157578493</v>
       </c>
       <c r="L743">
         <v>0.02550625207480358</v>
@@ -35702,7 +35702,7 @@
         <v>0.9337518585825225</v>
       </c>
       <c r="L747">
-        <v>0.02274198769828423</v>
+        <v>0.02282292003884752</v>
       </c>
       <c r="M747">
         <v>2.62</v>
@@ -36342,7 +36342,7 @@
         <v>9.513810082063305</v>
       </c>
       <c r="K761">
-        <v>0.9768856447688564</v>
+        <v>0.9756690997566898</v>
       </c>
       <c r="L761">
         <v>0.0246189917936694</v>
@@ -36389,7 +36389,7 @@
         <v>7.487754232599316</v>
       </c>
       <c r="K762">
-        <v>0.9425769514199929</v>
+        <v>0.942410157578499</v>
       </c>
       <c r="L762">
         <v>0.02550625207480358</v>
@@ -36486,7 +36486,7 @@
         <v>0.93375185858252</v>
       </c>
       <c r="L764">
-        <v>0.02274198769828423</v>
+        <v>0.02282292003884752</v>
       </c>
       <c r="M764">
         <v>4.13</v>
@@ -36624,10 +36624,10 @@
         <v>7.803655068078669</v>
       </c>
       <c r="K767">
-        <v>0.7123588456712674</v>
+        <v>0.7122471381527367</v>
       </c>
       <c r="L767">
-        <v>0.03963691376701967</v>
+        <v>0.03978819969742814</v>
       </c>
       <c r="M767">
         <v>2.45</v>
@@ -36671,7 +36671,7 @@
         <v>7.487754232599315</v>
       </c>
       <c r="K768">
-        <v>0.9425769514199906</v>
+        <v>0.9424101575785071</v>
       </c>
       <c r="L768">
         <v>0.02550625207480358</v>
@@ -36815,7 +36815,7 @@
         <v>0.9337518585825237</v>
       </c>
       <c r="L771">
-        <v>0.02274198769828423</v>
+        <v>0.02282292003884752</v>
       </c>
       <c r="M771">
         <v>52.97</v>
@@ -37880,7 +37880,7 @@
         <v>0.6135458167330677</v>
       </c>
       <c r="L795">
-        <v>0.04751735184196476</v>
+        <v>0.04805125467164976</v>
       </c>
       <c r="M795">
         <v>0.06</v>
@@ -37971,7 +37971,7 @@
         <v>17.87864406779661</v>
       </c>
       <c r="K797">
-        <v>0.9022222222222224</v>
+        <v>0.8982300884955751</v>
       </c>
       <c r="L797">
         <v>0.03813559322033899</v>
@@ -38632,7 +38632,7 @@
         <v>0.9380103934669638</v>
       </c>
       <c r="L811">
-        <v>0.03348937702556716</v>
+        <v>0.03384947785379906</v>
       </c>
       <c r="M811">
         <v>1.12</v>
@@ -39099,7 +39099,7 @@
         <v>22.00333773087071</v>
       </c>
       <c r="K821">
-        <v>0.9622093023255812</v>
+        <v>0.9578488372093024</v>
       </c>
       <c r="L821">
         <v>0.06200527704485488</v>
@@ -39616,7 +39616,7 @@
         <v>9.513810082063305</v>
       </c>
       <c r="K832">
-        <v>0.9768856447688564</v>
+        <v>0.975669099756692</v>
       </c>
       <c r="L832">
         <v>0.0246189917936694</v>
@@ -40277,7 +40277,7 @@
         <v>0.9337518585825241</v>
       </c>
       <c r="L846">
-        <v>0.02274198769828423</v>
+        <v>0.02282292003884752</v>
       </c>
       <c r="M846">
         <v>12.09</v>
@@ -40403,7 +40403,7 @@
         <v>884.5700000000001</v>
       </c>
       <c r="G849">
-        <v>0.9411764705882353</v>
+        <v>0.9142857142857143</v>
       </c>
       <c r="H849">
         <v>0.02380952380952381</v>
@@ -40462,7 +40462,7 @@
         <v>11.30720848056537</v>
       </c>
       <c r="K850">
-        <v>0.7919999999999999</v>
+        <v>0.788844621513944</v>
       </c>
       <c r="L850">
         <v>0.06007067137809187</v>
@@ -40999,7 +40999,7 @@
         <v>1409.98</v>
       </c>
       <c r="G862">
-        <v>0.7551020408163265</v>
+        <v>0.7474747474747475</v>
       </c>
       <c r="H862">
         <v>0.01869158878504673</v>
@@ -41105,7 +41105,7 @@
         <v>17.87864406779661</v>
       </c>
       <c r="K864">
-        <v>0.9022222222222215</v>
+        <v>0.8982300884955742</v>
       </c>
       <c r="L864">
         <v>0.03813559322033899</v>
@@ -41390,7 +41390,7 @@
         <v>0.9380103934669634</v>
       </c>
       <c r="L870">
-        <v>0.03348937702556716</v>
+        <v>0.03384947785379906</v>
       </c>
       <c r="M870">
         <v>1.19</v>
@@ -42139,7 +42139,7 @@
         <v>0.933349609375</v>
       </c>
       <c r="L886">
-        <v>0.03635084427767354</v>
+        <v>0.03658536585365853</v>
       </c>
       <c r="M886">
         <v>1.34</v>
@@ -42468,7 +42468,7 @@
         <v>0.9337518585825197</v>
       </c>
       <c r="L893">
-        <v>0.02274198769828423</v>
+        <v>0.02282292003884752</v>
       </c>
       <c r="M893">
         <v>2.03</v>
@@ -42890,7 +42890,7 @@
         <v>0.8821596244131457</v>
       </c>
       <c r="L903">
-        <v>0.0657030223390276</v>
+        <v>0.06614104248795445</v>
       </c>
       <c r="M903">
         <v>0.25</v>
@@ -42937,7 +42937,7 @@
         <v>0.6135458167330675</v>
       </c>
       <c r="L904">
-        <v>0.04751735184196476</v>
+        <v>0.04805125467164976</v>
       </c>
       <c r="M904">
         <v>0.84</v>
@@ -43169,7 +43169,7 @@
         <v>17.87864406779661</v>
       </c>
       <c r="K909">
-        <v>0.9022222222222237</v>
+        <v>0.8982300884955777</v>
       </c>
       <c r="L909">
         <v>0.03813559322033899</v>
@@ -43313,7 +43313,7 @@
         <v>0.9380103934669637</v>
       </c>
       <c r="L912">
-        <v>0.03348937702556716</v>
+        <v>0.03384947785379906</v>
       </c>
       <c r="M912">
         <v>0.34</v>
@@ -44300,7 +44300,7 @@
         <v>0.9337518585825222</v>
       </c>
       <c r="L933">
-        <v>0.02274198769828423</v>
+        <v>0.02282292003884752</v>
       </c>
       <c r="M933">
         <v>4.06</v>
@@ -44438,7 +44438,7 @@
         <v>17.87864406779661</v>
       </c>
       <c r="K936">
-        <v>0.9022222222222223</v>
+        <v>0.8982300884955752</v>
       </c>
       <c r="L936">
         <v>0.03813559322033899</v>
@@ -44485,7 +44485,7 @@
         <v>7.487754232599315</v>
       </c>
       <c r="K937">
-        <v>0.9425769514199874</v>
+        <v>0.9424101575785059</v>
       </c>
       <c r="L937">
         <v>0.02550625207480358</v>
@@ -44767,7 +44767,7 @@
         <v>7.487754232599315</v>
       </c>
       <c r="K943">
-        <v>0.9425769514199768</v>
+        <v>0.9424101575784889</v>
       </c>
       <c r="L943">
         <v>0.02550625207480358</v>
